--- a/output/yearly_surface_area_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_2_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449763257578</v>
+        <v>10.84497628318157</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907191940934</v>
+        <v>37.78907177105341</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.194427103169874</v>
+        <v>5.688246198406019</v>
       </c>
       <c r="C2" t="n">
-        <v>12.08924123009522</v>
+        <v>6.815292562881358</v>
       </c>
       <c r="D2" t="n">
-        <v>22.26800142772615</v>
+        <v>21.68975202992478</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.63357142660446</v>
+        <v>19.41896959000191</v>
       </c>
       <c r="C3" t="n">
-        <v>21.41682616814417</v>
+        <v>25.86414326838222</v>
       </c>
       <c r="D3" t="n">
-        <v>87.62589134254907</v>
+        <v>81.04327298557421</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.5351599764683</v>
+        <v>42.48709539668921</v>
       </c>
       <c r="C4" t="n">
-        <v>67.56584050167397</v>
+        <v>56.20701956353839</v>
       </c>
       <c r="D4" t="n">
-        <v>120.4162646643925</v>
+        <v>110.6400210255028</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.01313223971626</v>
+        <v>48.05655012288138</v>
       </c>
       <c r="C5" t="n">
-        <v>112.2628499806228</v>
+        <v>93.29057559605317</v>
       </c>
       <c r="D5" t="n">
-        <v>85.0929822655923</v>
+        <v>80.99418560036187</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>38.80259626265094</v>
       </c>
       <c r="C6" t="n">
-        <v>135.6078286399077</v>
+        <v>111.3360801478138</v>
       </c>
       <c r="D6" t="n">
-        <v>53.41394734495622</v>
+        <v>51.56237117474674</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.50602634051038</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>116.719002810199</v>
+        <v>112.8862597728195</v>
       </c>
       <c r="D7" t="n">
-        <v>40.66300816219864</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>73.43472827766142</v>
+        <v>81.44578954431539</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -912,7 +912,7 @@
         <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.655920417507819</v>
+        <v>7.669955978040563</v>
       </c>
       <c r="C21" t="n">
-        <v>92.8280350622823</v>
+        <v>94.91570522825198</v>
       </c>
       <c r="D21" t="n">
-        <v>7.655920417507819</v>
+        <v>7.669955978040563</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.834927516966294</v>
+        <v>6.847690237121502</v>
       </c>
       <c r="C2" t="n">
-        <v>13.01797455831271</v>
+        <v>8.213301293728815</v>
       </c>
       <c r="D2" t="n">
-        <v>19.90493470360408</v>
+        <v>23.28509204932585</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.83344704764331</v>
+        <v>19.09008410907923</v>
       </c>
       <c r="C3" t="n">
-        <v>33.89974822764236</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D3" t="n">
-        <v>84.91135894030663</v>
+        <v>79.32030576462104</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.01639627799848</v>
+        <v>39.34746623850791</v>
       </c>
       <c r="C4" t="n">
-        <v>60.03583561010095</v>
+        <v>59.69124216591032</v>
       </c>
       <c r="D4" t="n">
-        <v>132.0941536064083</v>
+        <v>123.6069447031947</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.75006491270713</v>
+        <v>54.92878405260905</v>
       </c>
       <c r="C5" t="n">
-        <v>117.8833555874358</v>
+        <v>98.1502267320749</v>
       </c>
       <c r="D5" t="n">
-        <v>104.9979169691964</v>
+        <v>97.9784208838317</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.3887817575443</v>
+        <v>50.95859633663495</v>
       </c>
       <c r="C6" t="n">
-        <v>153.9223320626319</v>
+        <v>127.5574974650838</v>
       </c>
       <c r="D6" t="n">
-        <v>64.56365602208724</v>
+        <v>63.31585468998956</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.77037851486003</v>
+        <v>34.37491411649782</v>
       </c>
       <c r="C7" t="n">
-        <v>152.1718759059598</v>
+        <v>134.9844188477109</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93302983859552</v>
+        <v>44.97484407925062</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.86352137357647</v>
+        <v>19.10971906316416</v>
       </c>
       <c r="C8" t="n">
-        <v>110.9865779651019</v>
+        <v>114.0741744949581</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01249464937726</v>
+        <v>71.55468142402876</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>38.57777603837842</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.82897755263721</v>
+        <v>7.847938343409245</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7980859902041</v>
+        <v>103.0041907572463</v>
       </c>
       <c r="D21" t="n">
-        <v>8.807599746716861</v>
+        <v>8.8289306363354</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.386088889676254</v>
+        <v>8.37823490804228</v>
       </c>
       <c r="C2" t="n">
-        <v>15.94849145548943</v>
+        <v>9.648616437337651</v>
       </c>
       <c r="D2" t="n">
-        <v>17.82461131830509</v>
+        <v>19.58979369054085</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.68404147014855</v>
+        <v>20.48907458763093</v>
       </c>
       <c r="C3" t="n">
-        <v>41.13522880794136</v>
+        <v>28.51977080836984</v>
       </c>
       <c r="D3" t="n">
-        <v>81.2298050493811</v>
+        <v>78.69198723390309</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.56144618030471</v>
+        <v>37.52239725631309</v>
       </c>
       <c r="C4" t="n">
-        <v>70.08009637225007</v>
+        <v>61.2993449054666</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5731076173605</v>
+        <v>130.5498644676281</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.97724954301564</v>
+        <v>56.18051237552373</v>
       </c>
       <c r="C5" t="n">
-        <v>114.4226949299658</v>
+        <v>102.1753923194868</v>
       </c>
       <c r="D5" t="n">
-        <v>123.2584242681871</v>
+        <v>115.1099183229385</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.19131160027045</v>
+        <v>60.17622553180826</v>
       </c>
       <c r="C6" t="n">
-        <v>166.5613520071054</v>
+        <v>140.1965174095573</v>
       </c>
       <c r="D6" t="n">
-        <v>77.52468921355364</v>
+        <v>74.94858323761002</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.45393695892307</v>
+        <v>45.09461729916874</v>
       </c>
       <c r="C7" t="n">
-        <v>180.7377888564293</v>
+        <v>155.585412673626</v>
       </c>
       <c r="D7" t="n">
-        <v>52.34089710421445</v>
+        <v>50.783845245279</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.04009709162065</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="C8" t="n">
-        <v>149.5398103108741</v>
+        <v>143.0308230317178</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.30937370002476</v>
+        <v>13.7562488319063</v>
       </c>
       <c r="C9" t="n">
-        <v>92.96561710594743</v>
+        <v>100.6203039559598</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>53.09782458418874</v>
+        <v>60.07314202286233</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>39.80397892098267</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.986610707456624</v>
+        <v>8.010972235367786</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8192445506644</v>
+        <v>111.152239765728</v>
       </c>
       <c r="D21" t="n">
-        <v>9.983263384320781</v>
+        <v>10.01371529420973</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.622289175772236</v>
+        <v>7.58400101530661</v>
       </c>
       <c r="C2" t="n">
-        <v>11.09963954421444</v>
+        <v>6.561019907481434</v>
       </c>
       <c r="D2" t="n">
-        <v>15.03939308135689</v>
+        <v>16.27541344100362</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.56685364044468</v>
+        <v>25.38799563182252</v>
       </c>
       <c r="C3" t="n">
-        <v>59.16502539643403</v>
+        <v>42.67166396508762</v>
       </c>
       <c r="D3" t="n">
-        <v>90.5711344552895</v>
+        <v>87.94495934642927</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.49165997784518</v>
+        <v>26.99315312826605</v>
       </c>
       <c r="C4" t="n">
-        <v>94.78872259273379</v>
+        <v>85.12734343524093</v>
       </c>
       <c r="D4" t="n">
-        <v>135.4124608467626</v>
+        <v>126.5934212195135</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.63681976935347</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>99.52467351802042</v>
+        <v>83.76762286485911</v>
       </c>
       <c r="D5" t="n">
-        <v>79.44793296617314</v>
+        <v>75.71729169003527</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.21641076775758</v>
+        <v>27.97490083251287</v>
       </c>
       <c r="C6" t="n">
-        <v>119.0241464197706</v>
+        <v>102.4807158555076</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>33.44912603139308</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="C7" t="n">
-        <v>105.1608870881013</v>
+        <v>100.5496181212541</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>29.16477905005999</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>68.51126354086365</v>
+        <v>74.10231671654924</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.515057691831081</v>
+        <v>4.548437113775472</v>
       </c>
       <c r="C2" t="n">
-        <v>5.397648877948964</v>
+        <v>3.07188856658827</v>
       </c>
       <c r="D2" t="n">
-        <v>10.51451791248334</v>
+        <v>11.46190444708151</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.33890824661017</v>
+        <v>26.4090132442392</v>
       </c>
       <c r="C3" t="n">
-        <v>52.29770020522759</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D3" t="n">
-        <v>84.13086951543042</v>
+        <v>81.98575078165113</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.08097064230052</v>
+        <v>36.36098972218912</v>
       </c>
       <c r="C4" t="n">
-        <v>122.1775200458113</v>
+        <v>97.69862278812133</v>
       </c>
       <c r="D4" t="n">
-        <v>147.0010107476919</v>
+        <v>140.8493796328814</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.34291735288518</v>
+        <v>38.28816046562561</v>
       </c>
       <c r="C5" t="n">
-        <v>135.5793579564845</v>
+        <v>119.0369091399258</v>
       </c>
       <c r="D5" t="n">
-        <v>101.8808680082128</v>
+        <v>95.79403224188253</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>33.6906359666378</v>
       </c>
       <c r="C6" t="n">
-        <v>141.122305494662</v>
+        <v>119.7486762255047</v>
       </c>
       <c r="D6" t="n">
-        <v>43.31078172055229</v>
+        <v>42.7070068824405</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>16.5287043486993</v>
       </c>
       <c r="C7" t="n">
-        <v>131.6307686900038</v>
+        <v>123.6059629554904</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>91.12582190818894</v>
+        <v>96.13273519984767</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>44.70780870369548</v>
+        <v>51.25312064790897</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.600469742100554</v>
+        <v>4.99218707609503</v>
       </c>
       <c r="C2" t="n">
-        <v>12.24828435818321</v>
+        <v>3.839615271309276</v>
       </c>
       <c r="D2" t="n">
-        <v>14.07433508808227</v>
+        <v>16.84875410028376</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.53816197284327</v>
+        <v>20.87195619228719</v>
       </c>
       <c r="C3" t="n">
-        <v>35.89760480578462</v>
+        <v>22.82563412373834</v>
       </c>
       <c r="D3" t="n">
-        <v>74.180856532889</v>
+        <v>73.57708169477721</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.9217886454923</v>
+        <v>43.45706212848506</v>
       </c>
       <c r="C4" t="n">
-        <v>126.2488277753228</v>
+        <v>92.31275488262334</v>
       </c>
       <c r="D4" t="n">
-        <v>154.2374730756951</v>
+        <v>148.3666218042992</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.82245220091413</v>
+        <v>45.87216148093222</v>
       </c>
       <c r="C5" t="n">
-        <v>179.8316357254095</v>
+        <v>148.9311267342412</v>
       </c>
       <c r="D5" t="n">
-        <v>126.5472790774139</v>
+        <v>119.7486762255047</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.60762938013333</v>
+        <v>41.74096714146165</v>
       </c>
       <c r="C6" t="n">
-        <v>174.853193117174</v>
+        <v>153.8015770950096</v>
       </c>
       <c r="D6" t="n">
-        <v>60.53849043467533</v>
+        <v>58.6064109527176</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>26.11056194214817</v>
       </c>
       <c r="C7" t="n">
-        <v>165.8260229766245</v>
+        <v>147.0216274494811</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>128.0935317116026</v>
+        <v>128.3438773761855</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>72.77499382040753</v>
+        <v>81.42811808563893</v>
       </c>
       <c r="D9" t="n">
         <v>29.17656002251095</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.756747553525043</v>
+        <v>2.95800583289564</v>
       </c>
       <c r="C2" t="n">
-        <v>5.820782138479339</v>
+        <v>1.785799074024948</v>
       </c>
       <c r="D2" t="n">
-        <v>9.860673941454964</v>
+        <v>11.64745476318416</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.54797944988574</v>
+        <v>21.08303194870025</v>
       </c>
       <c r="C3" t="n">
-        <v>43.17235529425349</v>
+        <v>20.84250376115979</v>
       </c>
       <c r="D3" t="n">
-        <v>72.11918635397069</v>
+        <v>73.00275928779283</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.68679109127881</v>
+        <v>47.89848874249763</v>
       </c>
       <c r="C4" t="n">
-        <v>126.5168448985822</v>
+        <v>89.05826124304515</v>
       </c>
       <c r="D4" t="n">
-        <v>160.9123757168692</v>
+        <v>157.1090851106171</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.245986372072</v>
+        <v>47.07480241863456</v>
       </c>
       <c r="C5" t="n">
-        <v>219.6415051326177</v>
+        <v>176.4691498383642</v>
       </c>
       <c r="D5" t="n">
-        <v>132.7813769993811</v>
+        <v>125.8600556844411</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>33.16736444027425</v>
       </c>
       <c r="C6" t="n">
-        <v>207.8192992780776</v>
+        <v>188.2167428673815</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>56.99634471775284</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.384125394267761</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>170.2576321135946</v>
+        <v>159.2983824910874</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>91.29271901791088</v>
+        <v>100.2217143880356</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.06249736236907</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.835287369864788</v>
+        <v>3.208351497478576</v>
       </c>
       <c r="C2" t="n">
-        <v>7.223699607848031</v>
+        <v>3.906374115198058</v>
       </c>
       <c r="D2" t="n">
-        <v>12.27184630308513</v>
+        <v>9.940195505498956</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.26126806251667</v>
+        <v>15.7423244375976</v>
       </c>
       <c r="C3" t="n">
-        <v>32.72655972106742</v>
+        <v>13.64629308903066</v>
       </c>
       <c r="D3" t="n">
-        <v>64.4664629993668</v>
+        <v>66.08634671137405</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.86172210908399</v>
+        <v>44.79714774478195</v>
       </c>
       <c r="C4" t="n">
-        <v>118.5146193612665</v>
+        <v>71.31808022730529</v>
       </c>
       <c r="D4" t="n">
-        <v>160.0955616269358</v>
+        <v>157.657882077291</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.30260894374884</v>
+        <v>57.82493978013714</v>
       </c>
       <c r="C5" t="n">
-        <v>227.3973119961675</v>
+        <v>172.1249162470721</v>
       </c>
       <c r="D5" t="n">
-        <v>154.1834769519616</v>
+        <v>150.3055735201867</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.66046382971341</v>
+        <v>45.16235789076178</v>
       </c>
       <c r="C6" t="n">
-        <v>269.4445844213541</v>
+        <v>231.0445047174444</v>
       </c>
       <c r="D6" t="n">
-        <v>79.81903359837844</v>
+        <v>76.31713953733006</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>226.6109320850658</v>
+        <v>210.8607536658342</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>41.80085375142069</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>143.0308230317178</v>
+        <v>146.285316671296</v>
       </c>
       <c r="D8" t="n">
         <v>32.96217917008666</v>
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>59.3515574602409</v>
+        <v>67.22811929141305</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.137264752145306</v>
+        <v>2.401354884587698</v>
       </c>
       <c r="C2" t="n">
-        <v>4.394302724208723</v>
+        <v>2.329687302177681</v>
       </c>
       <c r="D2" t="n">
-        <v>9.612291772280519</v>
+        <v>7.822565707438585</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.10142311317368</v>
+        <v>13.87209506100743</v>
       </c>
       <c r="C3" t="n">
-        <v>31.27357311878215</v>
+        <v>14.65258448588365</v>
       </c>
       <c r="D3" t="n">
-        <v>60.71127803062275</v>
+        <v>60.52474596681586</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.63726173770997</v>
+        <v>40.18980576875168</v>
       </c>
       <c r="C4" t="n">
-        <v>105.4838820827985</v>
+        <v>57.08764725424778</v>
       </c>
       <c r="D4" t="n">
-        <v>157.6961702377567</v>
+        <v>156.2795083005285</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.40769700583225</v>
+        <v>63.34727061652545</v>
       </c>
       <c r="C5" t="n">
-        <v>231.5697397392165</v>
+        <v>160.7366428778091</v>
       </c>
       <c r="D5" t="n">
-        <v>168.664255589602</v>
+        <v>166.209886328985</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.18123208132072</v>
+        <v>53.45419900083034</v>
       </c>
       <c r="C6" t="n">
-        <v>310.7025316923263</v>
+        <v>256.9665711003772</v>
       </c>
       <c r="D6" t="n">
-        <v>93.70585487494957</v>
+        <v>91.57251711362126</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>281.2874069776834</v>
+        <v>259.0694746828738</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>47.66974152740813</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>181.834401042073</v>
+        <v>187.0916599983147</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>65.45311944213483</v>
+        <v>77.76718089650257</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.877903431774901</v>
+        <v>3.402737542919445</v>
       </c>
       <c r="C2" t="n">
-        <v>14.46899766518949</v>
+        <v>6.634650985299944</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5736437589164</v>
+        <v>15.21708941582556</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.35743827980385</v>
+        <v>11.09374905798896</v>
       </c>
       <c r="C3" t="n">
-        <v>24.7940382707532</v>
+        <v>12.02150063850219</v>
       </c>
       <c r="D3" t="n">
-        <v>55.50310645959343</v>
+        <v>54.07957228843554</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.66430870507238</v>
+        <v>33.96159833300992</v>
       </c>
       <c r="C4" t="n">
-        <v>93.53797601752335</v>
+        <v>47.69428522001429</v>
       </c>
       <c r="D4" t="n">
-        <v>152.9101501795535</v>
+        <v>151.6721663244982</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.38315331322608</v>
+        <v>62.16917337142928</v>
       </c>
       <c r="C5" t="n">
-        <v>215.7145143156305</v>
+        <v>136.3402124272758</v>
       </c>
       <c r="D5" t="n">
-        <v>178.7026258655257</v>
+        <v>177.598159698248</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.72087452348698</v>
+        <v>65.77120569831082</v>
       </c>
       <c r="C6" t="n">
-        <v>333.4044656053296</v>
+        <v>257.3690876591183</v>
       </c>
       <c r="D6" t="n">
-        <v>115.3209940793516</v>
+        <v>114.6769675853657</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>32.75797564760332</v>
       </c>
       <c r="C7" t="n">
-        <v>345.0067599741183</v>
+        <v>306.0205768907733</v>
       </c>
       <c r="D7" t="n">
-        <v>56.65273302126644</v>
+        <v>58.4493313200381</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>253.5167096676538</v>
+        <v>251.8477385704343</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>118.9249899016416</v>
+        <v>135.4546759980451</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>53.38253141842032</v>
       </c>
       <c r="D10" t="n">
         <v>26.90479583488384</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.179120050529424</v>
+        <v>4.466952054322987</v>
       </c>
       <c r="C2" t="n">
-        <v>7.12552483742335</v>
+        <v>9.541605937574751</v>
       </c>
       <c r="D2" t="n">
-        <v>16.03684874887164</v>
+        <v>11.19486907152638</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.832342126752048</v>
+        <v>2.410190613925919</v>
       </c>
       <c r="C2" t="n">
-        <v>8.564766971849174</v>
+        <v>3.715915060574177</v>
       </c>
       <c r="D2" t="n">
-        <v>10.09923863358694</v>
+        <v>11.19977781004761</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.36787765165207</v>
+        <v>15.20236320026186</v>
       </c>
       <c r="C3" t="n">
-        <v>37.28677780729386</v>
+        <v>18.11324514335365</v>
       </c>
       <c r="D3" t="n">
-        <v>61.59975970296612</v>
+        <v>60.70146055358029</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.46982484864026</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="C4" t="n">
-        <v>131.5325939195792</v>
+        <v>70.47574069706152</v>
       </c>
       <c r="D4" t="n">
-        <v>157.351576793566</v>
+        <v>156.6879153454952</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.03581024790518</v>
+        <v>39.34353924769093</v>
       </c>
       <c r="C5" t="n">
-        <v>297.960428238907</v>
+        <v>211.7875234986432</v>
       </c>
       <c r="D5" t="n">
-        <v>163.8046044535803</v>
+        <v>163.8291481461865</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.99249017573129</v>
+        <v>20.32708621643021</v>
       </c>
       <c r="C6" t="n">
-        <v>286.0282666414913</v>
+        <v>254.5112200920559</v>
       </c>
       <c r="D6" t="n">
-        <v>88.19137802019524</v>
+        <v>89.68068928753766</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>178.282437848108</v>
+        <v>177.0847056489269</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>87.62098260402782</v>
+        <v>99.80447161373074</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.86766934857171</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
         <v>20.52343575727956</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.484443586550183</v>
+        <v>5.62050560681299</v>
       </c>
       <c r="C2" t="n">
-        <v>6.699446333780234</v>
+        <v>6.253732876052181</v>
       </c>
       <c r="D2" t="n">
-        <v>20.31923223479624</v>
+        <v>22.18455287286518</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.12596680577985</v>
+        <v>9.493500300066655</v>
       </c>
       <c r="C3" t="n">
-        <v>17.95616551067416</v>
+        <v>24.04300127700439</v>
       </c>
       <c r="D3" t="n">
-        <v>16.6062624173348</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39696619186238</v>
+        <v>13.39767531839651</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13705829857362</v>
+        <v>70.14077078454642</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576113669630868</v>
+        <v>1.576197096281942</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.649557127312894</v>
+        <v>4.354051068334604</v>
       </c>
       <c r="C2" t="n">
-        <v>8.653124265231387</v>
+        <v>3.646210973572654</v>
       </c>
       <c r="D2" t="n">
-        <v>28.98315572477433</v>
+        <v>30.31244211632452</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.70720250442297</v>
+        <v>15.42816517223863</v>
       </c>
       <c r="C3" t="n">
-        <v>23.06616231127881</v>
+        <v>24.25898577193868</v>
       </c>
       <c r="D3" t="n">
-        <v>29.65859814529614</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.26421330562941</v>
+        <v>11.15461741565226</v>
       </c>
       <c r="C4" t="n">
-        <v>27.92483169959628</v>
+        <v>37.19056653227767</v>
       </c>
       <c r="D4" t="n">
-        <v>23.7769476491535</v>
+        <v>21.64557338323367</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4376361591443</v>
+        <v>15.43862814010089</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12575962469975</v>
+        <v>86.13129383424706</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250028665083009</v>
+        <v>3.250237503179135</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.847870163570749</v>
+        <v>5.695118432335748</v>
       </c>
       <c r="C2" t="n">
-        <v>5.480115685105695</v>
+        <v>6.10647072041516</v>
       </c>
       <c r="D2" t="n">
-        <v>33.74266859496287</v>
+        <v>26.80269407364217</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.23948968657399</v>
+        <v>15.2367243699105</v>
       </c>
       <c r="C3" t="n">
-        <v>29.37389131106457</v>
+        <v>18.2359636063845</v>
       </c>
       <c r="D3" t="n">
-        <v>45.96051877431443</v>
+        <v>45.86234400388975</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.19735665074939</v>
+        <v>21.77320058478576</v>
       </c>
       <c r="C4" t="n">
-        <v>44.91201222617884</v>
+        <v>50.46379549369455</v>
       </c>
       <c r="D4" t="n">
-        <v>33.28517416478385</v>
+        <v>30.87302005544944</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.27813769993811</v>
+        <v>10.11200135374215</v>
       </c>
       <c r="C5" t="n">
-        <v>31.75953823238432</v>
+        <v>41.47884050442774</v>
       </c>
       <c r="D5" t="n">
-        <v>31.19503330244241</v>
+        <v>30.43417883165113</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>31.27455486648638</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7260954882316</v>
+        <v>16.72802556072086</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0291824782128</v>
+        <v>102.0409559203973</v>
       </c>
       <c r="D21" t="n">
-        <v>4.1815238720579</v>
+        <v>4.182006390180216</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.313218575383737</v>
+        <v>6.806456833543137</v>
       </c>
       <c r="C2" t="n">
-        <v>9.371763584740052</v>
+        <v>5.737333583618359</v>
       </c>
       <c r="D2" t="n">
-        <v>32.55377212511998</v>
+        <v>25.21717153128357</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.84679060487527</v>
+        <v>17.48492661263569</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74495088554086</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="D3" t="n">
-        <v>61.37886646951058</v>
+        <v>56.02834148136547</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.31146036862027</v>
+        <v>25.7168811127452</v>
       </c>
       <c r="C4" t="n">
-        <v>60.15070009149782</v>
+        <v>47.77086154094555</v>
       </c>
       <c r="D4" t="n">
-        <v>47.98782778358409</v>
+        <v>46.04789431999239</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.02260555939346</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>59.39573610693204</v>
+        <v>69.4095626902495</v>
       </c>
       <c r="D5" t="n">
-        <v>35.61289797155305</v>
+        <v>34.21390749300135</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83398682699105</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>32.00006641992479</v>
+        <v>39.80888765950392</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
         <v>33.7623035490478</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.74489413227862</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04324620136602</v>
+        <v>18.04838121887102</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7107014089116</v>
+        <v>117.7442012850157</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014415400455339</v>
+        <v>6.016127072957006</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.620325680363742</v>
+        <v>8.165195656220721</v>
       </c>
       <c r="C2" t="n">
-        <v>6.724971774090651</v>
+        <v>7.191301933607885</v>
       </c>
       <c r="D2" t="n">
-        <v>36.69772918474577</v>
+        <v>37.20725624324987</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.58033606639688</v>
+        <v>18.49121800948867</v>
       </c>
       <c r="C3" t="n">
-        <v>29.36898257254333</v>
+        <v>20.52343575727957</v>
       </c>
       <c r="D3" t="n">
-        <v>68.17746932141975</v>
+        <v>59.017763240797</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.71764187627119</v>
+        <v>22.05398042820035</v>
       </c>
       <c r="C4" t="n">
-        <v>51.05088062083414</v>
+        <v>42.18079011296421</v>
       </c>
       <c r="D4" t="n">
-        <v>58.37668198992384</v>
+        <v>54.81588306662066</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.08932334555324</v>
+        <v>18.26050729899067</v>
       </c>
       <c r="C5" t="n">
-        <v>63.86268816125503</v>
+        <v>59.07666810305183</v>
       </c>
       <c r="D5" t="n">
-        <v>35.61289797155305</v>
+        <v>34.18936380039518</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.20254312671111</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="C6" t="n">
-        <v>43.31078172055229</v>
+        <v>51.15985461600555</v>
       </c>
       <c r="D6" t="n">
-        <v>31.91956310817655</v>
+        <v>31.47679489356124</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>21.43940636534185</v>
+        <v>25.3919226226395</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.96089432274615</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.04792842882442</v>
+        <v>7.051914286494204</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07432902022893</v>
+        <v>66.99318572169494</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404955268015263</v>
+        <v>4.407446429058878</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.506622873120359</v>
+        <v>6.275331325545611</v>
       </c>
       <c r="C2" t="n">
-        <v>7.081346190732242</v>
+        <v>5.15221195188726</v>
       </c>
       <c r="D2" t="n">
-        <v>30.7503015924186</v>
+        <v>28.29200534098458</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.22185928562655</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="C3" t="n">
-        <v>27.39076094848601</v>
+        <v>25.40763058590746</v>
       </c>
       <c r="D3" t="n">
-        <v>82.53062075750812</v>
+        <v>76.0118160013093</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.61852641587127</v>
+        <v>30.69434197327653</v>
       </c>
       <c r="C4" t="n">
-        <v>65.0515846310979</v>
+        <v>48.06440410451534</v>
       </c>
       <c r="D4" t="n">
-        <v>80.55828961967627</v>
+        <v>72.5050132017397</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.20699420134261</v>
+        <v>26.65445017030091</v>
       </c>
       <c r="C5" t="n">
-        <v>82.29500130848889</v>
+        <v>70.73492209098271</v>
       </c>
       <c r="D5" t="n">
-        <v>48.89103567149117</v>
+        <v>47.49204519293946</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.50067563363265</v>
+        <v>18.67676832559133</v>
       </c>
       <c r="C6" t="n">
-        <v>76.96116603131597</v>
+        <v>76.3976428490783</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.37845589222053</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>44.79518424937346</v>
+        <v>53.65840252331367</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>24.61732368398877</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6185,7 +6185,7 @@
         <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
         <v>23.27821981539612</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264616362863566</v>
+        <v>7.271065154361485</v>
       </c>
       <c r="C21" t="n">
-        <v>75.3703947647095</v>
+        <v>76.3461841207956</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448462272147674</v>
+        <v>5.453298865771114</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.055018929166827</v>
+        <v>4.757549374780043</v>
       </c>
       <c r="C2" t="n">
-        <v>4.260785036431157</v>
+        <v>7.436738859669589</v>
       </c>
       <c r="D2" t="n">
-        <v>25.98980697452581</v>
+        <v>23.99096864867931</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.41544350981242</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="C3" t="n">
-        <v>27.44966581074082</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="D3" t="n">
-        <v>87.54244278768809</v>
+        <v>81.00891181592556</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.32270156172349</v>
+        <v>39.94731408580271</v>
       </c>
       <c r="C4" t="n">
-        <v>66.44272112801563</v>
+        <v>57.07488453409257</v>
       </c>
       <c r="D4" t="n">
-        <v>101.7699305176329</v>
+        <v>94.31650194699108</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.63744166415923</v>
+        <v>37.15915060574178</v>
       </c>
       <c r="C5" t="n">
-        <v>103.5743827980385</v>
+        <v>80.23333112957059</v>
       </c>
       <c r="D5" t="n">
-        <v>66.73430019617695</v>
+        <v>62.34097921967247</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.75855648468008</v>
+        <v>27.81389420901639</v>
       </c>
       <c r="C6" t="n">
-        <v>106.1436165400524</v>
+        <v>96.40271581851556</v>
       </c>
       <c r="D6" t="n">
-        <v>43.19002675292993</v>
+        <v>42.9082651618111</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>80.24805734513427</v>
+        <v>84.7994397020225</v>
       </c>
       <c r="D7" t="n">
-        <v>37.18958478457343</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>42.80910864368217</v>
+        <v>51.07051557491908</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.467482994053172</v>
+        <v>7.477529884633823</v>
       </c>
       <c r="C21" t="n">
-        <v>84.00918368309819</v>
+        <v>85.99159367328896</v>
       </c>
       <c r="D21" t="n">
-        <v>6.534047619796525</v>
+        <v>6.542838649054596</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_2_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497628318157</v>
+        <v>10.84497652584728</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907177105341</v>
+        <v>37.78907261661654</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.688246198406019</v>
+        <v>6.686683613625026</v>
       </c>
       <c r="C2" t="n">
-        <v>6.815292562881358</v>
+        <v>7.080364443027996</v>
       </c>
       <c r="D2" t="n">
-        <v>21.68975202992478</v>
+        <v>20.37617360164255</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.41896959000191</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="C3" t="n">
-        <v>25.86414326838222</v>
+        <v>30.65016332658542</v>
       </c>
       <c r="D3" t="n">
-        <v>81.04327298557421</v>
+        <v>56.6812037046896</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.48709539668921</v>
+        <v>43.24009588584652</v>
       </c>
       <c r="C4" t="n">
-        <v>56.20701956353839</v>
+        <v>65.57485615746145</v>
       </c>
       <c r="D4" t="n">
-        <v>110.6400210255028</v>
+        <v>67.65517954276044</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.05655012288138</v>
+        <v>54.60971604872884</v>
       </c>
       <c r="C5" t="n">
-        <v>93.29057559605317</v>
+        <v>89.92808970900784</v>
       </c>
       <c r="D5" t="n">
-        <v>80.99418560036187</v>
+        <v>52.20443417332415</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>50.79758971313847</v>
       </c>
       <c r="C6" t="n">
-        <v>111.3360801478138</v>
+        <v>116.7298020349458</v>
       </c>
       <c r="D6" t="n">
-        <v>51.56237117474674</v>
+        <v>41.94222542083224</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>34.6743471662931</v>
       </c>
       <c r="C7" t="n">
-        <v>112.8862597728195</v>
+        <v>103.4241753992887</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>17.85799074024948</v>
       </c>
       <c r="C8" t="n">
-        <v>81.44578954431539</v>
+        <v>61.08434215823654</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.669955978040563</v>
+        <v>7.708996852170187</v>
       </c>
       <c r="C21" t="n">
-        <v>94.91570522825198</v>
+        <v>95.39883604560606</v>
       </c>
       <c r="D21" t="n">
-        <v>7.669955978040563</v>
+        <v>8.672621458691459</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.847690237121502</v>
+        <v>8.874999246391166</v>
       </c>
       <c r="C2" t="n">
-        <v>8.213301293728815</v>
+        <v>14.56030020168444</v>
       </c>
       <c r="D2" t="n">
-        <v>23.28509204932585</v>
+        <v>31.11551173839841</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.09008410907923</v>
+        <v>22.75200304591983</v>
       </c>
       <c r="C3" t="n">
-        <v>26.01631416254048</v>
+        <v>28.858473766335</v>
       </c>
       <c r="D3" t="n">
-        <v>79.32030576462104</v>
+        <v>59.017763240797</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.34746623850791</v>
+        <v>43.80165557267569</v>
       </c>
       <c r="C4" t="n">
-        <v>59.69124216591032</v>
+        <v>70.48850341721673</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6069447031947</v>
+        <v>77.95469470801373</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.92878405260905</v>
+        <v>59.32210502911353</v>
       </c>
       <c r="C5" t="n">
-        <v>98.1502267320749</v>
+        <v>105.4151597435013</v>
       </c>
       <c r="D5" t="n">
-        <v>97.9784208838317</v>
+        <v>63.32272692391928</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.95859633663495</v>
+        <v>61.70578845502478</v>
       </c>
       <c r="C6" t="n">
-        <v>127.5574974650838</v>
+        <v>128.5637888619368</v>
       </c>
       <c r="D6" t="n">
-        <v>63.31585468998956</v>
+        <v>47.65796055495717</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.37491411649782</v>
+        <v>47.37030847761284</v>
       </c>
       <c r="C7" t="n">
-        <v>134.9844188477109</v>
+        <v>135.7030581672196</v>
       </c>
       <c r="D7" t="n">
-        <v>44.97484407925062</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.10971906316416</v>
+        <v>27.03733177495716</v>
       </c>
       <c r="C8" t="n">
-        <v>114.0741744949581</v>
+        <v>97.63480918734528</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>12.86874890726719</v>
       </c>
       <c r="C9" t="n">
-        <v>71.55468142402876</v>
+        <v>53.0281204971872</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.847938343409245</v>
+        <v>7.894697943761921</v>
       </c>
       <c r="C21" t="n">
-        <v>103.0041907572463</v>
+        <v>104.6047477548455</v>
       </c>
       <c r="D21" t="n">
-        <v>8.8289306363354</v>
+        <v>9.868372429702401</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.37823490804228</v>
+        <v>9.098837722959438</v>
       </c>
       <c r="C2" t="n">
-        <v>9.648616437337651</v>
+        <v>10.39670818797372</v>
       </c>
       <c r="D2" t="n">
-        <v>19.58979369054085</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.48907458763093</v>
+        <v>25.66779372753286</v>
       </c>
       <c r="C3" t="n">
-        <v>28.51977080836984</v>
+        <v>41.74882112309561</v>
       </c>
       <c r="D3" t="n">
-        <v>78.69198723390309</v>
+        <v>67.50497214401069</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.52239725631309</v>
+        <v>43.16351956491527</v>
       </c>
       <c r="C4" t="n">
-        <v>61.2993449054666</v>
+        <v>70.34811349550944</v>
       </c>
       <c r="D4" t="n">
-        <v>130.5498644676281</v>
+        <v>87.1693786600743</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.18051237552373</v>
+        <v>61.62921213409354</v>
       </c>
       <c r="C5" t="n">
-        <v>102.1753923194868</v>
+        <v>115.2080930933632</v>
       </c>
       <c r="D5" t="n">
-        <v>115.1099183229385</v>
+        <v>73.23837873681207</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.17622553180826</v>
+        <v>69.39385472698156</v>
       </c>
       <c r="C6" t="n">
-        <v>140.1965174095573</v>
+        <v>146.0732591671787</v>
       </c>
       <c r="D6" t="n">
-        <v>74.94858323761002</v>
+        <v>55.10451689166923</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.09461729916874</v>
+        <v>58.56910453995621</v>
       </c>
       <c r="C7" t="n">
-        <v>155.585412673626</v>
+        <v>157.1424645325614</v>
       </c>
       <c r="D7" t="n">
-        <v>50.783845245279</v>
+        <v>44.97484407925062</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.53664044579129</v>
+        <v>37.46840113257952</v>
       </c>
       <c r="C8" t="n">
-        <v>143.0308230317178</v>
+        <v>134.268724771315</v>
       </c>
       <c r="D8" t="n">
-        <v>41.47393176590651</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7562488319063</v>
+        <v>19.081248379741</v>
       </c>
       <c r="C9" t="n">
-        <v>100.6203039559598</v>
+        <v>81.7609305573786</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>60.07314202286233</v>
+        <v>46.6919208139783</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80397892098267</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.010972235367786</v>
+        <v>8.063437897767061</v>
       </c>
       <c r="C21" t="n">
-        <v>111.152239765728</v>
+        <v>112.8881305687388</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01371529420973</v>
+        <v>11.08722710942971</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.58400101530661</v>
+        <v>8.385107141972007</v>
       </c>
       <c r="C2" t="n">
-        <v>6.561019907481434</v>
+        <v>6.986116663420303</v>
       </c>
       <c r="D2" t="n">
-        <v>16.27541344100362</v>
+        <v>25.34676222824415</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.38799563182252</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C3" t="n">
-        <v>42.67166396508762</v>
+        <v>57.63840771633024</v>
       </c>
       <c r="D3" t="n">
-        <v>87.94495934642927</v>
+        <v>72.18790869326797</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.99315312826605</v>
+        <v>29.6095107600838</v>
       </c>
       <c r="C4" t="n">
-        <v>85.12734343524093</v>
+        <v>96.67760517570466</v>
       </c>
       <c r="D4" t="n">
-        <v>126.5934212195135</v>
+        <v>83.69791877785757</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>39.07355862902306</v>
       </c>
       <c r="C5" t="n">
-        <v>83.76762286485911</v>
+        <v>87.27737090754145</v>
       </c>
       <c r="D5" t="n">
-        <v>75.71729169003527</v>
+        <v>53.30890034060182</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.97490083251287</v>
+        <v>36.34724525432967</v>
       </c>
       <c r="C6" t="n">
-        <v>102.4807158555076</v>
+        <v>103.4870072523605</v>
       </c>
       <c r="D6" t="n">
-        <v>33.44912603139308</v>
+        <v>29.58496706747763</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="C7" t="n">
-        <v>100.5496181212541</v>
+        <v>94.38129729547136</v>
       </c>
       <c r="D7" t="n">
-        <v>29.16477905005999</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>74.10231671654924</v>
+        <v>60.24985660962675</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.548437113775472</v>
+        <v>5.226824777410018</v>
       </c>
       <c r="C2" t="n">
-        <v>3.07188856658827</v>
+        <v>3.140610905885546</v>
       </c>
       <c r="D2" t="n">
-        <v>11.46190444708151</v>
+        <v>18.72094697228243</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.4090132442392</v>
+        <v>30.66488954214912</v>
       </c>
       <c r="C3" t="n">
-        <v>34.94530953266521</v>
+        <v>42.75020378142736</v>
       </c>
       <c r="D3" t="n">
-        <v>81.98575078165113</v>
+        <v>75.44731107136738</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.36098972218912</v>
+        <v>42.34670547498192</v>
       </c>
       <c r="C4" t="n">
-        <v>97.69862278812133</v>
+        <v>122.4582998892259</v>
       </c>
       <c r="D4" t="n">
-        <v>140.8493796328814</v>
+        <v>98.73240312069322</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.28816046562561</v>
+        <v>43.63868545377073</v>
       </c>
       <c r="C5" t="n">
-        <v>119.0369091399258</v>
+        <v>131.3087554430109</v>
       </c>
       <c r="D5" t="n">
-        <v>95.79403224188253</v>
+        <v>66.14525157362885</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.6906359666378</v>
+        <v>43.55229165579701</v>
       </c>
       <c r="C6" t="n">
-        <v>119.7486762255047</v>
+        <v>123.8543451246649</v>
       </c>
       <c r="D6" t="n">
-        <v>42.7070068824405</v>
+        <v>35.62271544859552</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="C7" t="n">
-        <v>123.6059629554904</v>
+        <v>118.0365082292982</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>96.13273519984767</v>
+        <v>81.69613520889833</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>51.25312064790897</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.99218707609503</v>
+        <v>5.850234569606743</v>
       </c>
       <c r="C2" t="n">
-        <v>3.839615271309276</v>
+        <v>8.051312922528092</v>
       </c>
       <c r="D2" t="n">
-        <v>16.84875410028376</v>
+        <v>19.43860454408685</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.87195619228719</v>
+        <v>24.14117604742907</v>
       </c>
       <c r="C3" t="n">
-        <v>22.82563412373834</v>
+        <v>26.22738991895354</v>
       </c>
       <c r="D3" t="n">
-        <v>73.57708169477721</v>
+        <v>73.5918079103409</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.45706212848506</v>
+        <v>50.52760909447059</v>
       </c>
       <c r="C4" t="n">
-        <v>92.31275488262334</v>
+        <v>114.264633549582</v>
       </c>
       <c r="D4" t="n">
-        <v>148.3666218042992</v>
+        <v>110.6783091859684</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.87216148093222</v>
+        <v>52.84257018108458</v>
       </c>
       <c r="C5" t="n">
-        <v>148.9311267342412</v>
+        <v>179.8316357254095</v>
       </c>
       <c r="D5" t="n">
-        <v>119.7486762255047</v>
+        <v>84.30758410219485</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>50.75733805726436</v>
       </c>
       <c r="C6" t="n">
-        <v>153.8015770950096</v>
+        <v>163.9047427194135</v>
       </c>
       <c r="D6" t="n">
-        <v>58.6064109527176</v>
+        <v>46.32965591111124</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.11056194214817</v>
+        <v>34.97378021608837</v>
       </c>
       <c r="C7" t="n">
-        <v>147.0216274494811</v>
+        <v>148.3391328685803</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>16.1890196430299</v>
       </c>
       <c r="C8" t="n">
-        <v>128.3438773761855</v>
+        <v>116.4941825859265</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>81.42811808563893</v>
+        <v>67.44999427257284</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.95800583289564</v>
+        <v>3.491094836301658</v>
       </c>
       <c r="C2" t="n">
-        <v>1.785799074024948</v>
+        <v>3.762057202673777</v>
       </c>
       <c r="D2" t="n">
-        <v>11.64745476318416</v>
+        <v>13.54026433697201</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.08303194870025</v>
+        <v>24.47497026687298</v>
       </c>
       <c r="C3" t="n">
-        <v>20.84250376115979</v>
+        <v>29.88930885579414</v>
       </c>
       <c r="D3" t="n">
-        <v>73.00275928779283</v>
+        <v>74.3968410278233</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.89848874249763</v>
+        <v>55.60717171624359</v>
       </c>
       <c r="C4" t="n">
-        <v>89.05826124304515</v>
+        <v>108.4703585991173</v>
       </c>
       <c r="D4" t="n">
-        <v>157.1090851106171</v>
+        <v>120.0078576194259</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.07480241863456</v>
+        <v>55.0515025156399</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4691498383642</v>
+        <v>213.5792130588937</v>
       </c>
       <c r="D5" t="n">
-        <v>125.8600556844411</v>
+        <v>89.28995370124741</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.16736444027425</v>
+        <v>42.34474197957343</v>
       </c>
       <c r="C6" t="n">
-        <v>188.2167428673815</v>
+        <v>200.8155111559809</v>
       </c>
       <c r="D6" t="n">
-        <v>56.99634471775284</v>
+        <v>46.0478943199924</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>159.2983824910874</v>
+        <v>154.507453694363</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>100.2217143880356</v>
+        <v>86.20235717139117</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.208351497478576</v>
+        <v>4.221515128261284</v>
       </c>
       <c r="C2" t="n">
-        <v>3.906374115198058</v>
+        <v>9.283406291357839</v>
       </c>
       <c r="D2" t="n">
-        <v>9.940195505498956</v>
+        <v>11.2498469429642</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7423244375976</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="C3" t="n">
-        <v>13.64629308903066</v>
+        <v>22.02060100625596</v>
       </c>
       <c r="D3" t="n">
-        <v>66.08634671137405</v>
+        <v>68.48671984825749</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.79714774478195</v>
+        <v>51.45928766580082</v>
       </c>
       <c r="C4" t="n">
-        <v>71.31808022730529</v>
+        <v>92.49143296479625</v>
       </c>
       <c r="D4" t="n">
-        <v>157.657882077291</v>
+        <v>128.341913880777</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.82493978013714</v>
+        <v>67.37243620393737</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1249162470721</v>
+        <v>208.9159114637213</v>
       </c>
       <c r="D5" t="n">
-        <v>150.3055735201867</v>
+        <v>109.1458010196392</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.16235789076178</v>
+        <v>55.2252718592916</v>
       </c>
       <c r="C6" t="n">
-        <v>231.0445047174444</v>
+        <v>264.0508625342222</v>
       </c>
       <c r="D6" t="n">
-        <v>76.31713953733006</v>
+        <v>58.92842419971056</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="C7" t="n">
-        <v>210.8607536658342</v>
+        <v>215.4121360227224</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>146.285316671296</v>
+        <v>134.6025189907589</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>67.22811929141305</v>
+        <v>58.242182554442</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.401354884587698</v>
+        <v>3.119012456392117</v>
       </c>
       <c r="C2" t="n">
-        <v>2.329687302177681</v>
+        <v>5.660757262687108</v>
       </c>
       <c r="D2" t="n">
-        <v>7.822565707438585</v>
+        <v>8.249625958785947</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.87209506100743</v>
+        <v>16.90569546713007</v>
       </c>
       <c r="C3" t="n">
-        <v>14.65258448588365</v>
+        <v>28.96646601380214</v>
       </c>
       <c r="D3" t="n">
-        <v>60.52474596681586</v>
+        <v>63.28836575427063</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.18980576875168</v>
+        <v>46.00960615952677</v>
       </c>
       <c r="C4" t="n">
-        <v>57.08764725424778</v>
+        <v>78.13337279018666</v>
       </c>
       <c r="D4" t="n">
-        <v>156.2795083005285</v>
+        <v>132.3494080095125</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.34727061652545</v>
+        <v>73.53290304808611</v>
       </c>
       <c r="C5" t="n">
-        <v>160.7366428778091</v>
+        <v>201.2582793705962</v>
       </c>
       <c r="D5" t="n">
-        <v>166.209886328985</v>
+        <v>123.7738418129166</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.45419900083034</v>
+        <v>65.44919245131787</v>
       </c>
       <c r="C6" t="n">
-        <v>256.9665711003772</v>
+        <v>299.3113130799507</v>
       </c>
       <c r="D6" t="n">
-        <v>91.57251711362126</v>
+        <v>69.71586797397451</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="C7" t="n">
-        <v>259.0694746828738</v>
+        <v>273.5620342929652</v>
       </c>
       <c r="D7" t="n">
-        <v>47.66974152740813</v>
+        <v>43.47767883027424</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>187.0916599983147</v>
+        <v>174.4909282143068</v>
       </c>
       <c r="D8" t="n">
         <v>34.38080460272329</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>77.76718089650257</v>
+        <v>68.00468172547228</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.402737542919445</v>
+        <v>4.955862411037899</v>
       </c>
       <c r="C2" t="n">
-        <v>6.634650985299944</v>
+        <v>8.469537444537233</v>
       </c>
       <c r="D2" t="n">
-        <v>15.21708941582556</v>
+        <v>12.3886742798905</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.09374905798896</v>
+        <v>13.83282515283756</v>
       </c>
       <c r="C3" t="n">
-        <v>12.02150063850219</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D3" t="n">
-        <v>54.07957228843554</v>
+        <v>56.59284641130738</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.96159833300992</v>
+        <v>39.74311056331938</v>
       </c>
       <c r="C4" t="n">
-        <v>47.69428522001429</v>
+        <v>75.31281163588557</v>
       </c>
       <c r="D4" t="n">
-        <v>151.6721663244982</v>
+        <v>132.9620185769625</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.16917337142928</v>
+        <v>71.74121348783568</v>
       </c>
       <c r="C5" t="n">
-        <v>136.3402124272758</v>
+        <v>176.4936935309703</v>
       </c>
       <c r="D5" t="n">
-        <v>177.598159698248</v>
+        <v>137.5673970575843</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.77120569831082</v>
+        <v>78.0479607399172</v>
       </c>
       <c r="C6" t="n">
-        <v>257.3690876591183</v>
+        <v>308.569193930998</v>
       </c>
       <c r="D6" t="n">
-        <v>114.6769675853657</v>
+        <v>85.45426542075514</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.75797564760332</v>
+        <v>39.76470901281281</v>
       </c>
       <c r="C7" t="n">
-        <v>306.0205768907733</v>
+        <v>337.4011605093183</v>
       </c>
       <c r="D7" t="n">
-        <v>58.4493313200381</v>
+        <v>50.06520592577034</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>251.8477385704343</v>
+        <v>249.010487705161</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>135.4546759980451</v>
+        <v>121.5874896755589</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>53.38253141842032</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>20.61179305066178</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.466952054322987</v>
+        <v>6.845726741713008</v>
       </c>
       <c r="C2" t="n">
-        <v>9.541605937574751</v>
+        <v>2.797980957103409</v>
       </c>
       <c r="D2" t="n">
-        <v>11.19486907152638</v>
+        <v>9.75366344169206</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.410190613925919</v>
+        <v>3.586324363613598</v>
       </c>
       <c r="C2" t="n">
-        <v>3.715915060574177</v>
+        <v>4.878304342402401</v>
       </c>
       <c r="D2" t="n">
-        <v>11.19977781004761</v>
+        <v>9.216647447469056</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.20236320026186</v>
+        <v>18.71211124294421</v>
       </c>
       <c r="C3" t="n">
-        <v>18.11324514335365</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D3" t="n">
-        <v>60.70146055358029</v>
+        <v>61.23160431387356</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.90299657039137</v>
+        <v>54.76483218599983</v>
       </c>
       <c r="C4" t="n">
-        <v>70.47574069706152</v>
+        <v>107.7428835502704</v>
       </c>
       <c r="D4" t="n">
-        <v>156.6879153454952</v>
+        <v>135.8719187723501</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.34353924769093</v>
+        <v>45.28311285838414</v>
       </c>
       <c r="C5" t="n">
-        <v>211.7875234986432</v>
+        <v>262.8629478120835</v>
       </c>
       <c r="D5" t="n">
-        <v>163.8291481461865</v>
+        <v>124.5592399763141</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.32708621643021</v>
+        <v>24.67426505083509</v>
       </c>
       <c r="C6" t="n">
-        <v>254.5112200920559</v>
+        <v>279.6685050133804</v>
       </c>
       <c r="D6" t="n">
-        <v>89.68068928753766</v>
+        <v>70.56115274733101</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>177.0847056489269</v>
+        <v>175.1084475202781</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>99.80447161373074</v>
+        <v>89.62374792069132</v>
       </c>
       <c r="D8" t="n">
-        <v>24.86766934857171</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
         <v>16.52575910558656</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.62050560681299</v>
+        <v>7.064656479760047</v>
       </c>
       <c r="C2" t="n">
-        <v>6.253732876052181</v>
+        <v>7.199155915241861</v>
       </c>
       <c r="D2" t="n">
-        <v>22.18455287286518</v>
+        <v>8.700248155035233</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.493500300066655</v>
+        <v>14.53968349989526</v>
       </c>
       <c r="C3" t="n">
-        <v>24.04300127700439</v>
+        <v>7.048948516492098</v>
       </c>
       <c r="D3" t="n">
-        <v>12.541826921753</v>
+        <v>11.32936850700819</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39767531839651</v>
+        <v>13.39867240477907</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14077078454642</v>
+        <v>70.14599082501985</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576197096281942</v>
+        <v>1.576314400562244</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.354051068334604</v>
+        <v>5.380959166976768</v>
       </c>
       <c r="C2" t="n">
-        <v>3.646210973572654</v>
+        <v>8.22115527536279</v>
       </c>
       <c r="D2" t="n">
-        <v>30.31244211632452</v>
+        <v>12.33271466074843</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.42816517223863</v>
+        <v>20.47925711058846</v>
       </c>
       <c r="C3" t="n">
-        <v>24.25898577193868</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D3" t="n">
-        <v>28.14670668075605</v>
+        <v>15.89940407027709</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.15461741565226</v>
+        <v>16.84679060487526</v>
       </c>
       <c r="C4" t="n">
-        <v>37.19056653227767</v>
+        <v>11.46092269937727</v>
       </c>
       <c r="D4" t="n">
-        <v>21.64557338323367</v>
+        <v>21.00743737547325</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43862814010089</v>
+        <v>15.44434654229269</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13129383424706</v>
+        <v>86.16319649910658</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250237503179135</v>
+        <v>3.251441377324777</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.695118432335748</v>
+        <v>7.074473956802516</v>
       </c>
       <c r="C2" t="n">
-        <v>6.10647072041516</v>
+        <v>5.141412727140546</v>
       </c>
       <c r="D2" t="n">
-        <v>26.80269407364217</v>
+        <v>18.02292435456295</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2367243699105</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2359636063845</v>
+        <v>27.43984833369835</v>
       </c>
       <c r="D3" t="n">
-        <v>45.86234400388975</v>
+        <v>22.07459712998953</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.77320058478576</v>
+        <v>29.68608708101505</v>
       </c>
       <c r="C4" t="n">
-        <v>50.46379549369455</v>
+        <v>34.68907338185679</v>
       </c>
       <c r="D4" t="n">
-        <v>30.87302005544944</v>
+        <v>24.26193101505142</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.11200135374215</v>
+        <v>14.7753029489145</v>
       </c>
       <c r="C5" t="n">
-        <v>41.47884050442774</v>
+        <v>14.5298660228528</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43417883165113</v>
+        <v>29.99239236474006</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72802556072086</v>
+        <v>16.74255991384373</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0409559203973</v>
+        <v>102.1296154744468</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182006390180216</v>
+        <v>5.02276797415312</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.806456833543137</v>
+        <v>6.90364985626357</v>
       </c>
       <c r="C2" t="n">
-        <v>5.737333583618359</v>
+        <v>6.205627238544088</v>
       </c>
       <c r="D2" t="n">
-        <v>25.21717153128357</v>
+        <v>14.73701478844887</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48492661263569</v>
+        <v>22.17277190041422</v>
       </c>
       <c r="C3" t="n">
-        <v>21.3775562599743</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D3" t="n">
-        <v>56.02834148136547</v>
+        <v>30.86123908299849</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.7168811127452</v>
+        <v>34.11475097487241</v>
       </c>
       <c r="C4" t="n">
-        <v>47.77086154094555</v>
+        <v>54.02459441699773</v>
       </c>
       <c r="D4" t="n">
-        <v>46.04789431999239</v>
+        <v>29.32873091666921</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.3775562599743</v>
+        <v>30.01693605734623</v>
       </c>
       <c r="C5" t="n">
-        <v>69.4095626902495</v>
+        <v>41.77336481570179</v>
       </c>
       <c r="D5" t="n">
-        <v>34.21390749300135</v>
+        <v>32.10314992887071</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.781152377410974</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>39.80888765950392</v>
+        <v>17.83148355223482</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04838121887102</v>
+        <v>18.07445468188553</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7442012850157</v>
+        <v>117.9142995913485</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016127072957006</v>
+        <v>6.885506545480201</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.165195656220721</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C2" t="n">
-        <v>7.191301933607885</v>
+        <v>4.494440990041897</v>
       </c>
       <c r="D2" t="n">
-        <v>37.20725624324987</v>
+        <v>23.15255610925253</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.49121800948867</v>
+        <v>20.59215809657685</v>
       </c>
       <c r="C3" t="n">
-        <v>20.52343575727957</v>
+        <v>22.26603793231766</v>
       </c>
       <c r="D3" t="n">
-        <v>59.017763240797</v>
+        <v>33.11435006424491</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.05398042820035</v>
+        <v>28.65230674844316</v>
       </c>
       <c r="C4" t="n">
-        <v>42.18079011296421</v>
+        <v>47.01786105178824</v>
       </c>
       <c r="D4" t="n">
-        <v>54.81588306662066</v>
+        <v>32.65980087717864</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.26050729899067</v>
+        <v>24.93639168786899</v>
       </c>
       <c r="C5" t="n">
-        <v>59.07666810305183</v>
+        <v>54.33973543006097</v>
       </c>
       <c r="D5" t="n">
-        <v>34.18936380039518</v>
+        <v>28.81429511964389</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.50568218314512</v>
+        <v>14.77235770580176</v>
       </c>
       <c r="C6" t="n">
-        <v>51.15985461600555</v>
+        <v>29.54471541160352</v>
       </c>
       <c r="D6" t="n">
-        <v>31.47679489356124</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>25.3919226226395</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051914286494204</v>
+        <v>7.066984164463589</v>
       </c>
       <c r="C21" t="n">
-        <v>66.99318572169494</v>
+        <v>66.25297654184615</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407446429058878</v>
+        <v>5.300238123347691</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.275331325545611</v>
+        <v>6.952737241475911</v>
       </c>
       <c r="C2" t="n">
-        <v>5.15221195188726</v>
+        <v>9.896998606512096</v>
       </c>
       <c r="D2" t="n">
-        <v>28.29200534098458</v>
+        <v>19.77436225893926</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.54369260617026</v>
+        <v>22.59492341324034</v>
       </c>
       <c r="C3" t="n">
-        <v>25.40763058590746</v>
+        <v>19.19807635654638</v>
       </c>
       <c r="D3" t="n">
-        <v>76.0118160013093</v>
+        <v>45.17021187239575</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.69434197327653</v>
+        <v>36.34822700203391</v>
       </c>
       <c r="C4" t="n">
-        <v>48.06440410451534</v>
+        <v>52.71003424101125</v>
       </c>
       <c r="D4" t="n">
-        <v>72.5050132017397</v>
+        <v>42.94655332227672</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.65445017030091</v>
+        <v>35.93196597543326</v>
       </c>
       <c r="C5" t="n">
-        <v>70.73492209098271</v>
+        <v>74.14649536324036</v>
       </c>
       <c r="D5" t="n">
-        <v>47.49204519293946</v>
+        <v>34.77841242294326</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.67676832559133</v>
+        <v>25.84156307118455</v>
       </c>
       <c r="C6" t="n">
-        <v>76.3976428490783</v>
+        <v>64.0403844957237</v>
       </c>
       <c r="D6" t="n">
-        <v>35.74347041621788</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>12.93550775115597</v>
       </c>
       <c r="C7" t="n">
-        <v>53.65840252331367</v>
+        <v>31.79978988825843</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>27.53802310412303</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.271065154361485</v>
+        <v>7.293628920404153</v>
       </c>
       <c r="C21" t="n">
-        <v>76.3461841207956</v>
+        <v>76.58310366424361</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453298865771114</v>
+        <v>6.381925305353634</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.757549374780043</v>
+        <v>6.711227306231195</v>
       </c>
       <c r="C2" t="n">
-        <v>7.436738859669589</v>
+        <v>7.81471172580461</v>
       </c>
       <c r="D2" t="n">
-        <v>23.99096864867931</v>
+        <v>22.91006442630357</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.16924582022473</v>
+        <v>23.52758373227481</v>
       </c>
       <c r="C3" t="n">
-        <v>22.19731559302038</v>
+        <v>31.12140222462389</v>
       </c>
       <c r="D3" t="n">
-        <v>81.00891181592556</v>
+        <v>50.50601064497716</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.94731408580271</v>
+        <v>41.1214843400819</v>
       </c>
       <c r="C4" t="n">
-        <v>57.07488453409257</v>
+        <v>49.99157484795184</v>
       </c>
       <c r="D4" t="n">
-        <v>94.31650194699108</v>
+        <v>55.53059539531234</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.15915060574178</v>
+        <v>46.16668579220627</v>
       </c>
       <c r="C5" t="n">
-        <v>80.23333112957059</v>
+        <v>87.03193398147975</v>
       </c>
       <c r="D5" t="n">
-        <v>62.34097921967247</v>
+        <v>42.87783098297945</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.81389420901639</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="C6" t="n">
-        <v>96.40271581851556</v>
+        <v>94.75239792767668</v>
       </c>
       <c r="D6" t="n">
-        <v>42.9082651618111</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="C7" t="n">
-        <v>84.7994397020225</v>
+        <v>65.99504417487908</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>51.07051557491908</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.96093538047515</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.477529884633823</v>
+        <v>7.508328661878296</v>
       </c>
       <c r="C21" t="n">
-        <v>85.99159367328896</v>
+        <v>86.34577961160041</v>
       </c>
       <c r="D21" t="n">
-        <v>6.542838649054596</v>
+        <v>7.508328661878296</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_2_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497652584728</v>
+        <v>10.84497640704945</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907261661654</v>
+        <v>37.78907220266821</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.686683613625026</v>
+        <v>1.022981107825176</v>
       </c>
       <c r="C2" t="n">
-        <v>7.080364443027996</v>
+        <v>3.161227607674729</v>
       </c>
       <c r="D2" t="n">
-        <v>20.37617360164255</v>
+        <v>13.24279478258523</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.16924582022473</v>
+        <v>7.775441817634739</v>
       </c>
       <c r="C3" t="n">
-        <v>30.65016332658542</v>
+        <v>36.2706689333984</v>
       </c>
       <c r="D3" t="n">
-        <v>56.6812037046896</v>
+        <v>60.47565858160353</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.24009588584652</v>
+        <v>13.33704256219292</v>
       </c>
       <c r="C4" t="n">
-        <v>65.57485615746145</v>
+        <v>124.5130978342145</v>
       </c>
       <c r="D4" t="n">
-        <v>67.65517954276044</v>
+        <v>71.21597846606362</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.60971604872884</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="C5" t="n">
-        <v>89.92808970900784</v>
+        <v>169.5478285234242</v>
       </c>
       <c r="D5" t="n">
-        <v>52.20443417332415</v>
+        <v>45.33220024359647</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.79758971313847</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>116.7298020349458</v>
+        <v>123.3713252541754</v>
       </c>
       <c r="D6" t="n">
-        <v>41.94222542083224</v>
+        <v>29.14219885286233</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.6743471662931</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>103.4241753992887</v>
+        <v>62.70128062713103</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>29.70375853969149</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.85799074024948</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>61.08434215823654</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.64235040268046</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.708996852170187</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.39883604560606</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.672621458691459</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.874999246391166</v>
+        <v>1.611047982669016</v>
       </c>
       <c r="C2" t="n">
-        <v>14.56030020168444</v>
+        <v>5.547856276698725</v>
       </c>
       <c r="D2" t="n">
-        <v>31.11551173839841</v>
+        <v>15.92492951058751</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.75200304591983</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C3" t="n">
-        <v>28.858473766335</v>
+        <v>22.61946710584651</v>
       </c>
       <c r="D3" t="n">
-        <v>59.017763240797</v>
+        <v>57.66786014745765</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.80165557267569</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C4" t="n">
-        <v>70.48850341721673</v>
+        <v>107.1557984231308</v>
       </c>
       <c r="D4" t="n">
-        <v>77.95469470801373</v>
+        <v>83.91488502049611</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.32210502911353</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="C5" t="n">
-        <v>105.4151597435013</v>
+        <v>200.9146676741098</v>
       </c>
       <c r="D5" t="n">
-        <v>63.32272692391928</v>
+        <v>58.90486225480863</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.70578845502478</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="C6" t="n">
-        <v>128.5637888619368</v>
+        <v>197.5148753743031</v>
       </c>
       <c r="D6" t="n">
-        <v>47.65796055495717</v>
+        <v>35.66296710446964</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.37030847761284</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>135.7030581672196</v>
+        <v>118.9348073786841</v>
       </c>
       <c r="D7" t="n">
-        <v>41.86074036137975</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.03733177495716</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>97.63480918734528</v>
+        <v>55.91053175685585</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.86874890726719</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
         <v>36.0546844384641</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59188035913637</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>44.53403936004381</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.894697943761921</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6047477548455</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.868372429702401</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.098837722959438</v>
+        <v>0.8757189521881549</v>
       </c>
       <c r="C2" t="n">
-        <v>10.39670818797372</v>
+        <v>2.471058971589222</v>
       </c>
       <c r="D2" t="n">
-        <v>31.03599017435442</v>
+        <v>10.89445427402685</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.66779372753286</v>
+        <v>6.013204688511713</v>
       </c>
       <c r="C3" t="n">
-        <v>41.74882112309561</v>
+        <v>23.6699371493906</v>
       </c>
       <c r="D3" t="n">
-        <v>67.50497214401069</v>
+        <v>58.82632243846888</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.16351956491527</v>
+        <v>15.5577558691992</v>
       </c>
       <c r="C4" t="n">
-        <v>70.34811349550944</v>
+        <v>97.57099558656925</v>
       </c>
       <c r="D4" t="n">
-        <v>87.1693786600743</v>
+        <v>92.35104304308896</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.62921213409354</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="C5" t="n">
-        <v>115.2080930933632</v>
+        <v>229.3117200194488</v>
       </c>
       <c r="D5" t="n">
-        <v>73.23837873681207</v>
+        <v>66.41523219229673</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.39385472698156</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>146.0732591671787</v>
+        <v>240.8659087507295</v>
       </c>
       <c r="D6" t="n">
-        <v>55.10451689166923</v>
+        <v>36.38749691020379</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.56910453995621</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>157.1424645325614</v>
+        <v>108.6941970756856</v>
       </c>
       <c r="D7" t="n">
-        <v>44.97484407925062</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.46840113257952</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>134.268724771315</v>
+        <v>44.56152829576272</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.081248379741</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>81.7609305573786</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>39.93749660876023</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.063437897767061</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.8881305687388</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08722710942971</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.385107141972007</v>
+        <v>0.6371542600561799</v>
       </c>
       <c r="C2" t="n">
-        <v>6.986116663420303</v>
+        <v>4.165555509119216</v>
       </c>
       <c r="D2" t="n">
-        <v>25.34676222824415</v>
+        <v>9.774280143481244</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.54217107911827</v>
+        <v>4.511130701014094</v>
       </c>
       <c r="C3" t="n">
-        <v>57.63840771633024</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="D3" t="n">
-        <v>72.18790869326797</v>
+        <v>54.14829462773282</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.6095107600838</v>
+        <v>13.80926320793563</v>
       </c>
       <c r="C4" t="n">
-        <v>96.67760517570466</v>
+        <v>77.54628766304705</v>
       </c>
       <c r="D4" t="n">
-        <v>83.69791877785757</v>
+        <v>100.8893028269235</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.07355862902306</v>
+        <v>20.15037162966578</v>
       </c>
       <c r="C5" t="n">
-        <v>87.27737090754145</v>
+        <v>206.7315228217722</v>
       </c>
       <c r="D5" t="n">
-        <v>53.30890034060182</v>
+        <v>81.4605157598791</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>16.14091400552181</v>
       </c>
       <c r="C6" t="n">
-        <v>103.4870072523605</v>
+        <v>304.2220150965932</v>
       </c>
       <c r="D6" t="n">
-        <v>29.58496706747763</v>
+        <v>46.32965591111124</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.79305652304895</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>94.38129729547136</v>
+        <v>215.9511155123539</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>60.24985660962675</v>
+        <v>86.20235717139117</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>37.71874679716245</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.226824777410018</v>
+        <v>0.3279037332184347</v>
       </c>
       <c r="C2" t="n">
-        <v>3.140610905885546</v>
+        <v>3.201479263548849</v>
       </c>
       <c r="D2" t="n">
-        <v>18.72094697228243</v>
+        <v>8.223118770771283</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.66488954214912</v>
+        <v>3.539200473809752</v>
       </c>
       <c r="C3" t="n">
-        <v>42.75020378142736</v>
+        <v>16.36573422979433</v>
       </c>
       <c r="D3" t="n">
-        <v>75.44731107136738</v>
+        <v>50.43728830567989</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.34670547498192</v>
+        <v>12.1118214272929</v>
       </c>
       <c r="C4" t="n">
-        <v>122.4582998892259</v>
+        <v>62.44798971943536</v>
       </c>
       <c r="D4" t="n">
-        <v>98.73240312069322</v>
+        <v>104.5266780711579</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.63868545377073</v>
+        <v>21.47573103039898</v>
       </c>
       <c r="C5" t="n">
-        <v>131.3087554430109</v>
+        <v>187.685617359384</v>
       </c>
       <c r="D5" t="n">
-        <v>66.14525157362885</v>
+        <v>94.59139130418019</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.55229165579701</v>
+        <v>19.32079481957723</v>
       </c>
       <c r="C6" t="n">
-        <v>123.8543451246649</v>
+        <v>328.5742669004353</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>55.4667817945363</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.2360046641135</v>
+        <v>7.845145904636261</v>
       </c>
       <c r="C7" t="n">
-        <v>118.0365082292982</v>
+        <v>297.6963381064646</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>81.69613520889833</v>
+        <v>132.1825108997905</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49062147687869</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.850234569606743</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C2" t="n">
-        <v>8.051312922528092</v>
+        <v>17.64298799301943</v>
       </c>
       <c r="D2" t="n">
-        <v>19.43860454408685</v>
+        <v>9.090001993621218</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.14117604742907</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C3" t="n">
-        <v>26.22738991895354</v>
+        <v>14.31388152791849</v>
       </c>
       <c r="D3" t="n">
-        <v>73.5918079103409</v>
+        <v>45.93106634318703</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.52760909447059</v>
+        <v>9.661379157492862</v>
       </c>
       <c r="C4" t="n">
-        <v>114.264633549582</v>
+        <v>52.56964431930395</v>
       </c>
       <c r="D4" t="n">
-        <v>110.6783091859684</v>
+        <v>105.4328312021777</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.84257018108458</v>
+        <v>20.2240027074843</v>
       </c>
       <c r="C5" t="n">
-        <v>179.8316357254095</v>
+        <v>154.5761760336603</v>
       </c>
       <c r="D5" t="n">
-        <v>84.30758410219485</v>
+        <v>107.0350434555085</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.75733805726436</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="C6" t="n">
-        <v>163.9047427194135</v>
+        <v>317.0220416645631</v>
       </c>
       <c r="D6" t="n">
-        <v>46.32965591111124</v>
+        <v>68.10580173900973</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.97378021608837</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="C7" t="n">
-        <v>148.3391328685803</v>
+        <v>377.2856427420492</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.1890196430299</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4941825859265</v>
+        <v>237.3276900246239</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>67.44999427257284</v>
+        <v>93.74217954000666</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.491094836301658</v>
+        <v>0.6852598975642736</v>
       </c>
       <c r="C2" t="n">
-        <v>3.762057202673777</v>
+        <v>9.597565556716818</v>
       </c>
       <c r="D2" t="n">
-        <v>13.54026433697201</v>
+        <v>6.617961274327748</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.47497026687298</v>
+        <v>3.676645152404305</v>
       </c>
       <c r="C3" t="n">
-        <v>29.88930885579414</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D3" t="n">
-        <v>74.3968410278233</v>
+        <v>49.70097752749478</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.60717171624359</v>
+        <v>14.57502641724815</v>
       </c>
       <c r="C4" t="n">
-        <v>108.4703585991173</v>
+        <v>78.60559343592936</v>
       </c>
       <c r="D4" t="n">
-        <v>120.0078576194259</v>
+        <v>107.959849792909</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.0515025156399</v>
+        <v>14.06353586333556</v>
       </c>
       <c r="C5" t="n">
-        <v>213.5792130588937</v>
+        <v>249.7320722677824</v>
       </c>
       <c r="D5" t="n">
-        <v>89.28995370124741</v>
+        <v>98.02750826904405</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.34474197957343</v>
+        <v>8.332092765942681</v>
       </c>
       <c r="C6" t="n">
-        <v>200.8155111559809</v>
+        <v>319.9604125433738</v>
       </c>
       <c r="D6" t="n">
-        <v>46.0478943199924</v>
+        <v>58.92842419971056</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71970318267092</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>154.507453694363</v>
+        <v>166.9039819558875</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>86.20235717139117</v>
+        <v>69.09540342489051</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.06405994715006</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>23.91537407545231</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.221515128261284</v>
+        <v>0.3789546138392688</v>
       </c>
       <c r="C2" t="n">
-        <v>9.283406291357839</v>
+        <v>4.060508504764808</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2498469429642</v>
+        <v>5.119814277647116</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.44213062427633</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="C3" t="n">
-        <v>22.02060100625596</v>
+        <v>36.03504948437918</v>
       </c>
       <c r="D3" t="n">
-        <v>68.48671984825749</v>
+        <v>43.94793598060846</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.45928766580082</v>
+        <v>10.21017612416683</v>
       </c>
       <c r="C4" t="n">
-        <v>92.49143296479625</v>
+        <v>79.57556016772521</v>
       </c>
       <c r="D4" t="n">
-        <v>128.341913880777</v>
+        <v>103.6588131006037</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.37243620393737</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="C5" t="n">
-        <v>208.9159114637213</v>
+        <v>180.1016163440774</v>
       </c>
       <c r="D5" t="n">
-        <v>109.1458010196392</v>
+        <v>100.6291396852981</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.2252718592916</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>264.0508625342222</v>
+        <v>296.5742004805105</v>
       </c>
       <c r="D6" t="n">
-        <v>58.92842419971056</v>
+        <v>61.70578845502478</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.41566449399068</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C7" t="n">
-        <v>215.4121360227224</v>
+        <v>210.9206402757932</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>134.6025189907589</v>
+        <v>82.11337798320321</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>58.242182554442</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>17.0824100538945</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.119012456392117</v>
+        <v>0.2552544031041707</v>
       </c>
       <c r="C2" t="n">
-        <v>5.660757262687108</v>
+        <v>6.992988897350031</v>
       </c>
       <c r="D2" t="n">
-        <v>8.249625958785947</v>
+        <v>6.53745796257951</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90569546713007</v>
+        <v>2.091122610045706</v>
       </c>
       <c r="C3" t="n">
-        <v>28.96646601380214</v>
+        <v>24.47497026687298</v>
       </c>
       <c r="D3" t="n">
-        <v>63.28836575427063</v>
+        <v>38.06235849364884</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.00960615952677</v>
+        <v>7.9256492163845</v>
       </c>
       <c r="C4" t="n">
-        <v>78.13337279018666</v>
+        <v>85.49746231974197</v>
       </c>
       <c r="D4" t="n">
-        <v>132.3494080095125</v>
+        <v>102.4335919657037</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.53290304808611</v>
+        <v>14.87347771933918</v>
       </c>
       <c r="C5" t="n">
-        <v>201.2582793705962</v>
+        <v>162.307439204604</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7738418129166</v>
+        <v>114.6190444708151</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.44919245131787</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>299.3113130799507</v>
+        <v>295.6484123954057</v>
       </c>
       <c r="D6" t="n">
-        <v>69.71586797397451</v>
+        <v>77.72594749292425</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>273.5620342929652</v>
+        <v>323.4475803888584</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>174.4909282143068</v>
+        <v>177.4950761893021</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>68.00468172547228</v>
+        <v>65.23124446097505</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.955862411037899</v>
+        <v>0.4466952054322987</v>
       </c>
       <c r="C2" t="n">
-        <v>8.469537444537233</v>
+        <v>19.17353266394021</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3886742798905</v>
+        <v>7.797040267128168</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.83282515283756</v>
+        <v>1.467712817848982</v>
       </c>
       <c r="C3" t="n">
-        <v>25.53525778745954</v>
+        <v>25.77578597500001</v>
       </c>
       <c r="D3" t="n">
-        <v>56.59284641130738</v>
+        <v>34.77350368442202</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.74311056331938</v>
+        <v>5.92190215201676</v>
       </c>
       <c r="C4" t="n">
-        <v>75.31281163588557</v>
+        <v>73.00275928779283</v>
       </c>
       <c r="D4" t="n">
-        <v>132.9620185769625</v>
+        <v>97.76243638889737</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.74121348783568</v>
+        <v>13.69538047424301</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4936935309703</v>
+        <v>158.3559046950105</v>
       </c>
       <c r="D5" t="n">
-        <v>137.5673970575843</v>
+        <v>124.5592399763141</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>78.0479607399172</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="C6" t="n">
-        <v>308.569193930998</v>
+        <v>279.1049818311428</v>
       </c>
       <c r="D6" t="n">
-        <v>85.45426542075514</v>
+        <v>93.5850999073272</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.76470901281281</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>337.4011605093183</v>
+        <v>375.7884774930728</v>
       </c>
       <c r="D7" t="n">
-        <v>50.06520592577034</v>
+        <v>51.86180422454201</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>249.010487705161</v>
+        <v>295.1575385432823</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.7952820603647</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>121.5874896755589</v>
+        <v>135.4546759980451</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>24.29531043699581</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>48.54251523648354</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.845726741713008</v>
+        <v>3.742422248588841</v>
       </c>
       <c r="C2" t="n">
-        <v>2.797980957103409</v>
+        <v>20.84643075197677</v>
       </c>
       <c r="D2" t="n">
-        <v>9.75366344169206</v>
+        <v>11.40987181875643</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.586324363613598</v>
+        <v>0.5753041546886308</v>
       </c>
       <c r="C2" t="n">
-        <v>4.878304342402401</v>
+        <v>18.50790772046087</v>
       </c>
       <c r="D2" t="n">
-        <v>9.216647447469056</v>
+        <v>8.535314540721769</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.71211124294421</v>
+        <v>1.45298660228528</v>
       </c>
       <c r="C3" t="n">
-        <v>31.54355373745002</v>
+        <v>48.64069000690822</v>
       </c>
       <c r="D3" t="n">
-        <v>61.23160431387356</v>
+        <v>33.03090150938393</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.76483218599983</v>
+        <v>4.403138453546945</v>
       </c>
       <c r="C4" t="n">
-        <v>107.7428835502704</v>
+        <v>68.82934979703964</v>
       </c>
       <c r="D4" t="n">
-        <v>135.8719187723501</v>
+        <v>93.65284049892024</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.28311285838414</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="C5" t="n">
-        <v>262.8629478120835</v>
+        <v>145.9367962362884</v>
       </c>
       <c r="D5" t="n">
-        <v>124.5592399763141</v>
+        <v>129.885221271853</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.67426505083509</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>279.6685050133804</v>
+        <v>268.5590479921235</v>
       </c>
       <c r="D6" t="n">
-        <v>70.56115274733101</v>
+        <v>106.3046231635489</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.126506585127596</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>175.1084475202781</v>
+        <v>387.7657994848839</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>63.30014672672159</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>89.62374792069132</v>
+        <v>384.5309407993907</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>230.97185538733</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>92.10266087391453</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.064656479760047</v>
+        <v>4.410010687476672</v>
       </c>
       <c r="C2" t="n">
-        <v>7.199155915241861</v>
+        <v>12.60564052252905</v>
       </c>
       <c r="D2" t="n">
-        <v>8.700248155035233</v>
+        <v>17.50848855753762</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.53968349989526</v>
+        <v>6.042657119639118</v>
       </c>
       <c r="C3" t="n">
-        <v>7.048948516492098</v>
+        <v>41.15977250054753</v>
       </c>
       <c r="D3" t="n">
-        <v>11.32936850700819</v>
+        <v>10.80413348523615</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39867240477907</v>
+        <v>11.67666812858032</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14599082501985</v>
+        <v>59.94022972671229</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576314400562244</v>
+        <v>0.7784445419053544</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.380959166976768</v>
+        <v>2.180461651132166</v>
       </c>
       <c r="C2" t="n">
-        <v>8.22115527536279</v>
+        <v>6.405903770210438</v>
       </c>
       <c r="D2" t="n">
-        <v>12.33271466074843</v>
+        <v>18.02783309308418</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.47925711058846</v>
+        <v>11.94296082216245</v>
       </c>
       <c r="C3" t="n">
-        <v>20.42526098685489</v>
+        <v>46.49066253460771</v>
       </c>
       <c r="D3" t="n">
-        <v>15.89940407027709</v>
+        <v>23.49322256262617</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.84679060487526</v>
+        <v>7.466191290796993</v>
       </c>
       <c r="C4" t="n">
-        <v>11.46092269937727</v>
+        <v>66.36614480708438</v>
       </c>
       <c r="D4" t="n">
-        <v>21.00743737547325</v>
+        <v>19.92260616228052</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44434654229269</v>
+        <v>13.62309741461229</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16319649910658</v>
+        <v>73.72499777319592</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251441377324777</v>
+        <v>1.602717342895564</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.074473956802516</v>
+        <v>1.491274762750905</v>
       </c>
       <c r="C2" t="n">
-        <v>5.141412727140546</v>
+        <v>8.668832228499335</v>
       </c>
       <c r="D2" t="n">
-        <v>18.02292435456295</v>
+        <v>20.63928198638069</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.65949777754238</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C3" t="n">
-        <v>27.43984833369835</v>
+        <v>33.03581024790517</v>
       </c>
       <c r="D3" t="n">
-        <v>22.07459712998953</v>
+        <v>32.95727043156543</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.68608708101505</v>
+        <v>16.73192612347839</v>
       </c>
       <c r="C4" t="n">
-        <v>34.68907338185679</v>
+        <v>96.89457141834319</v>
       </c>
       <c r="D4" t="n">
-        <v>24.26193101505142</v>
+        <v>27.60576369571606</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.7753029489145</v>
+        <v>7.166758241001717</v>
       </c>
       <c r="C5" t="n">
-        <v>14.5298660228528</v>
+        <v>74.39193228930206</v>
       </c>
       <c r="D5" t="n">
-        <v>29.99239236474006</v>
+        <v>27.34167356327368</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74255991384373</v>
+        <v>14.82452968079596</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1296154744468</v>
+        <v>87.30000812024286</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02276797415312</v>
+        <v>2.470754946799326</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.90364985626357</v>
+        <v>1.422552423453628</v>
       </c>
       <c r="C2" t="n">
-        <v>6.205627238544088</v>
+        <v>6.89775937003809</v>
       </c>
       <c r="D2" t="n">
-        <v>14.73701478844887</v>
+        <v>22.42802630351838</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.17277190041422</v>
+        <v>7.03913103944963</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04652735719387</v>
+        <v>33.4285093296039</v>
       </c>
       <c r="D3" t="n">
-        <v>30.86123908299849</v>
+        <v>41.82245220091412</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.11475097487241</v>
+        <v>17.71465557542945</v>
       </c>
       <c r="C4" t="n">
-        <v>54.02459441699773</v>
+        <v>88.75195595932014</v>
       </c>
       <c r="D4" t="n">
-        <v>29.32873091666921</v>
+        <v>37.91804158112456</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.01693605734623</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C5" t="n">
-        <v>41.77336481570179</v>
+        <v>133.0022702328367</v>
       </c>
       <c r="D5" t="n">
-        <v>32.10314992887071</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.92078153559227</v>
+        <v>7.245298057341462</v>
       </c>
       <c r="C6" t="n">
-        <v>17.83148355223482</v>
+        <v>68.2265567066321</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>33.08686112852601</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07445468188553</v>
+        <v>16.05160507995057</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9142995913485</v>
+        <v>100.5337370796904</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885506545480201</v>
+        <v>3.379285279989593</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.725953521794898</v>
+        <v>1.646390900021901</v>
       </c>
       <c r="C2" t="n">
-        <v>4.494440990041897</v>
+        <v>7.702792487520473</v>
       </c>
       <c r="D2" t="n">
-        <v>23.15255610925253</v>
+        <v>22.35341347799562</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.59215809657685</v>
+        <v>5.856125055832224</v>
       </c>
       <c r="C3" t="n">
-        <v>22.26603793231766</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D3" t="n">
-        <v>33.11435006424491</v>
+        <v>49.06775025825559</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.65230674844316</v>
+        <v>15.60880674982004</v>
       </c>
       <c r="C4" t="n">
-        <v>47.01786105178824</v>
+        <v>85.94415752517426</v>
       </c>
       <c r="D4" t="n">
-        <v>32.65980087717864</v>
+        <v>48.63872651149973</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.93639168786899</v>
+        <v>21.18120671912494</v>
       </c>
       <c r="C5" t="n">
-        <v>54.33973543006097</v>
+        <v>149.0293015046659</v>
       </c>
       <c r="D5" t="n">
-        <v>28.81429511964389</v>
+        <v>37.45367491701582</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.77235770580176</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="C6" t="n">
-        <v>29.54471541160352</v>
+        <v>138.7877094539631</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>15.27108553955913</v>
+        <v>57.9103518304066</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066984164463589</v>
+        <v>17.2975978406296</v>
       </c>
       <c r="C21" t="n">
-        <v>66.25297654184615</v>
+        <v>113.2992658561239</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300238123347691</v>
+        <v>4.324399460157401</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.952737241475911</v>
+        <v>2.197151362104361</v>
       </c>
       <c r="C2" t="n">
-        <v>9.896998606512096</v>
+        <v>9.875400157018666</v>
       </c>
       <c r="D2" t="n">
-        <v>19.77436225893926</v>
+        <v>23.35185089321463</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.59492341324034</v>
+        <v>5.659775514982861</v>
       </c>
       <c r="C3" t="n">
-        <v>19.19807635654638</v>
+        <v>29.63896319121121</v>
       </c>
       <c r="D3" t="n">
-        <v>45.17021187239575</v>
+        <v>54.29555678336985</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.34822700203391</v>
+        <v>13.42638160327938</v>
       </c>
       <c r="C4" t="n">
-        <v>52.71003424101125</v>
+        <v>79.90739089176064</v>
       </c>
       <c r="D4" t="n">
-        <v>42.94655332227672</v>
+        <v>60.03583561010095</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.93196597543326</v>
+        <v>22.16295442337175</v>
       </c>
       <c r="C5" t="n">
-        <v>74.14649536324036</v>
+        <v>151.9745446174063</v>
       </c>
       <c r="D5" t="n">
-        <v>34.77841242294326</v>
+        <v>44.54680208019903</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.84156307118455</v>
+        <v>20.85035774279376</v>
       </c>
       <c r="C6" t="n">
-        <v>64.0403844957237</v>
+        <v>185.0771137092002</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.93550775115597</v>
+        <v>11.73777555197486</v>
       </c>
       <c r="C7" t="n">
-        <v>31.79978988825843</v>
+        <v>122.8274370260227</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>20.02765316663493</v>
+        <v>49.06775025825559</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.2611134982632</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.293628920404153</v>
+        <v>17.67293856473488</v>
       </c>
       <c r="C21" t="n">
-        <v>76.58310366424361</v>
+        <v>125.4778638096176</v>
       </c>
       <c r="D21" t="n">
-        <v>6.381925305353634</v>
+        <v>5.301881569420463</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.711227306231195</v>
+        <v>1.959568417676633</v>
       </c>
       <c r="C2" t="n">
-        <v>7.81471172580461</v>
+        <v>6.319509972236719</v>
       </c>
       <c r="D2" t="n">
-        <v>22.91006442630357</v>
+        <v>18.619826958745</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.52758373227481</v>
+        <v>8.207410807503335</v>
       </c>
       <c r="C3" t="n">
-        <v>31.12140222462389</v>
+        <v>47.56076753223673</v>
       </c>
       <c r="D3" t="n">
-        <v>50.50601064497716</v>
+        <v>59.07666810305182</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.1214843400819</v>
+        <v>10.64410860944392</v>
       </c>
       <c r="C4" t="n">
-        <v>49.99157484795184</v>
+        <v>123.4155039008665</v>
       </c>
       <c r="D4" t="n">
-        <v>55.53059539531234</v>
+        <v>55.90071427981338</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.16668579220627</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>87.03193398147975</v>
+        <v>110.5938788834032</v>
       </c>
       <c r="D5" t="n">
-        <v>42.87783098297945</v>
+        <v>36.1528592088888</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.7220929509027</v>
+        <v>7.285549713215581</v>
       </c>
       <c r="C6" t="n">
-        <v>94.75239792767668</v>
+        <v>80.86557665110554</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>25.1170332654504</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.63713856452295</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>65.99504417487908</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>27.36818075128833</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>32.62838495064274</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>24.96093538047515</v>
+        <v>25.18281036163492</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.508328661878296</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.34577961160041</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.508328661878296</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
